--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260827.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>24,954,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>24,954,004</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>8,984,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>8,984,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
